--- a/apps/admin-web/public/zone-list-template.xlsx
+++ b/apps/admin-web/public/zone-list-template.xlsx
@@ -1,171 +1,62 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="0" activeTab="0"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Table 1" state="visible" r:id="rId4"/>
+    <sheet name="Table 1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <definedNames/>
+  <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
-  <si>
-    <t>Name Of Your Unit</t>
-  </si>
-  <si>
-    <t>Zone No.</t>
-  </si>
-  <si>
-    <t>Zone Discription(Name)</t>
-  </si>
-  <si>
-    <t>Leader</t>
-  </si>
-  <si>
-    <t>Mobile No.</t>
-  </si>
-  <si>
-    <t>Zone 01</t>
-  </si>
-  <si>
-    <t>Zone 02</t>
-  </si>
-  <si>
-    <t>Zone 03</t>
-  </si>
-  <si>
-    <t>Zone 04</t>
-  </si>
-  <si>
-    <t>Zone 05</t>
-  </si>
-  <si>
-    <t>Zone 06</t>
-  </si>
-  <si>
-    <t>Zone 07</t>
-  </si>
-  <si>
-    <t>Zone 08</t>
-  </si>
-  <si>
-    <t>Zone 09</t>
-  </si>
-  <si>
-    <t>Zone 10</t>
-  </si>
-  <si>
-    <t>Zone 11</t>
-  </si>
-  <si>
-    <t>Zone 12</t>
-  </si>
-  <si>
-    <t>Zone 13</t>
-  </si>
-  <si>
-    <t>Zone 14</t>
-  </si>
-  <si>
-    <t>Zone 15</t>
-  </si>
-  <si>
-    <t>Zone 16</t>
-  </si>
-  <si>
-    <t>Zone 17</t>
-  </si>
-  <si>
-    <t>Zone 18</t>
-  </si>
-  <si>
-    <t>Zone 19</t>
-  </si>
-  <si>
-    <t>Zone 20</t>
-  </si>
-  <si>
-    <t>Zone 21</t>
-  </si>
-  <si>
-    <t>Zone 22</t>
-  </si>
-  <si>
-    <t>Zone 23</t>
-  </si>
-  <si>
-    <t>Zone 24</t>
-  </si>
-  <si>
-    <t>Zone 25</t>
-  </si>
-  <si>
-    <t>Zone 26</t>
-  </si>
-  <si>
-    <t>Zone 27</t>
-  </si>
-  <si>
-    <t>Zone 28</t>
-  </si>
-  <si>
-    <t>Zone 29</t>
-  </si>
-  <si>
-    <t>Zone 30</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="6">
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <color theme="1"/>
-      <family val="2"/>
+      <sz val="11"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <name val="Times New Roman"/>
       <charset val="204"/>
       <color rgb="FF000000"/>
       <sz val="10"/>
-      <name val="Times New Roman"/>
     </font>
     <font>
-      <b/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <b val="1"/>
       <color rgb="FFFFC000"/>
-      <family val="2"/>
       <sz val="16"/>
-      <name val="Arial"/>
     </font>
     <font>
-      <b/>
+      <name val="Arial"/>
+      <b val="1"/>
       <sz val="11"/>
-      <name val="Arial"/>
     </font>
     <font>
-      <b/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <b val="1"/>
       <color rgb="FFFFFFFF"/>
-      <family val="2"/>
       <sz val="11"/>
-      <name val="Arial"/>
     </font>
     <font>
+      <name val="Arial"/>
       <sz val="11"/>
-      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="7">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -194,7 +85,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -273,147 +164,216 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="43">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="4"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="4"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="4"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -737,286 +697,320 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
-  <sheetFormatPr defaultRowHeight="12.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
+  <dimension ref="A1:C32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75" customHeight="1" outlineLevelRow="0"/>
   <cols>
-    <col min="1" max="1" width="16.1640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="46.6640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="32.6640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="20" customWidth="1"/>
+    <col width="16.1640625" customWidth="1" style="1" min="1" max="1"/>
+    <col width="46.6640625" customWidth="1" style="1" min="2" max="2"/>
+    <col width="32.6640625" customWidth="1" style="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="33.95" customHeight="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-    </row>
-    <row r="2" ht="30.95" customHeight="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" ht="51.95" customHeight="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="7"/>
-    </row>
-    <row r="4" ht="51.95" customHeight="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="9"/>
-    </row>
-    <row r="5" ht="51.95" customHeight="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="7"/>
-    </row>
-    <row r="6" ht="51.95" customHeight="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="11"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="12"/>
-    </row>
-    <row r="7" ht="51.95" customHeight="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="7"/>
-    </row>
-    <row r="8" ht="51.95" customHeight="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="12"/>
-    </row>
-    <row r="9" ht="51.95" customHeight="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="14"/>
-    </row>
-    <row r="10" ht="51.95" customHeight="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="16"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="18"/>
-    </row>
-    <row r="11" ht="51.95" customHeight="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="14"/>
-    </row>
-    <row r="12" ht="51.95" customHeight="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="9"/>
-    </row>
-    <row r="13" ht="51.95" customHeight="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="7"/>
-    </row>
-    <row r="14" ht="51.95" customHeight="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="9"/>
-    </row>
-    <row r="15" ht="51.95" customHeight="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="B15" s="13"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="20"/>
-    </row>
-    <row r="16" ht="51.95" customHeight="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="9"/>
-    </row>
-    <row r="17" ht="51.95" customHeight="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="B17" s="13"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="14"/>
-    </row>
-    <row r="18" ht="51.95" customHeight="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="B18" s="11"/>
-      <c r="C18" s="21"/>
-      <c r="D18" s="22"/>
-    </row>
-    <row r="19" ht="51.95" customHeight="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19" s="6"/>
-      <c r="C19" s="23"/>
-      <c r="D19" s="24"/>
-    </row>
-    <row r="20" ht="51.95" customHeight="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="B20" s="26"/>
-      <c r="C20" s="26"/>
-      <c r="D20" s="27"/>
-    </row>
-    <row r="21" ht="51.95" customHeight="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B21" s="6"/>
-      <c r="C21" s="28"/>
-      <c r="D21" s="29"/>
-    </row>
-    <row r="22" ht="51.95" customHeight="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B22" s="30"/>
-      <c r="C22" s="31"/>
-      <c r="D22" s="32"/>
-    </row>
-    <row r="23" ht="51.95" customHeight="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="B23" s="13"/>
-      <c r="C23" s="33"/>
-      <c r="D23" s="34"/>
-    </row>
-    <row r="24" ht="51.95" customHeight="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="B24" s="11"/>
-      <c r="C24" s="35"/>
-      <c r="D24" s="36"/>
-    </row>
-    <row r="25" ht="51.95" customHeight="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B25" s="37"/>
-      <c r="C25" s="28"/>
-      <c r="D25" s="29"/>
-    </row>
-    <row r="26" ht="51.95" customHeight="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B26" s="8"/>
-      <c r="C26" s="31"/>
-      <c r="D26" s="32"/>
-    </row>
-    <row r="27" ht="51.95" customHeight="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="23"/>
-      <c r="D27" s="24"/>
-    </row>
-    <row r="28" ht="51.95" customHeight="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="38" t="s">
-        <v>30</v>
-      </c>
-      <c r="B28" s="39"/>
-      <c r="C28" s="40"/>
-      <c r="D28" s="41"/>
-    </row>
-    <row r="29" ht="51.95" customHeight="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B29" s="6"/>
-      <c r="C29" s="6"/>
-      <c r="D29" s="7"/>
-    </row>
-    <row r="30" ht="51.95" customHeight="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B30" s="8"/>
-      <c r="C30" s="8"/>
-      <c r="D30" s="9"/>
-    </row>
-    <row r="31" ht="51.95" customHeight="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B31" s="6"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="7"/>
-    </row>
-    <row r="32" ht="51.95" customHeight="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B32" s="8"/>
-      <c r="C32" s="8"/>
-      <c r="D32" s="9"/>
+    <row r="1" ht="33.95" customFormat="1" customHeight="1" s="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Name Of Your Unit</t>
+        </is>
+      </c>
+      <c r="B1" s="42" t="n"/>
+      <c r="C1" s="42" t="n"/>
+    </row>
+    <row r="2" ht="30.95" customFormat="1" customHeight="1" s="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Zone No.</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Zone Discription(Name)</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="51.95" customFormat="1" customHeight="1" s="1">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Zone 01</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="n"/>
+      <c r="C3" s="6" t="n"/>
+    </row>
+    <row r="4" ht="51.95" customFormat="1" customHeight="1" s="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Zone 02</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="n"/>
+      <c r="C4" s="8" t="n"/>
+    </row>
+    <row r="5" ht="51.95" customFormat="1" customHeight="1" s="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Zone 03</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n"/>
+    </row>
+    <row r="6" ht="51.95" customFormat="1" customHeight="1" s="1">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>Zone 04</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="n"/>
+      <c r="C6" s="11" t="n"/>
+    </row>
+    <row r="7" ht="51.95" customFormat="1" customHeight="1" s="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Zone 05</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+    </row>
+    <row r="8" ht="51.95" customFormat="1" customHeight="1" s="1">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>Zone 06</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="n"/>
+      <c r="C8" s="11" t="n"/>
+    </row>
+    <row r="9" ht="51.95" customFormat="1" customHeight="1" s="1">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Zone 07</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="n"/>
+      <c r="C9" s="13" t="n"/>
+    </row>
+    <row r="10" ht="51.95" customFormat="1" customHeight="1" s="1">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>Zone 08</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="n"/>
+      <c r="C10" s="17" t="n"/>
+    </row>
+    <row r="11" ht="51.95" customFormat="1" customHeight="1" s="1">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>Zone 09</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="n"/>
+      <c r="C11" s="13" t="n"/>
+    </row>
+    <row r="12" ht="51.95" customFormat="1" customHeight="1" s="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Zone 10</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="n"/>
+      <c r="C12" s="8" t="n"/>
+    </row>
+    <row r="13" ht="51.95" customFormat="1" customHeight="1" s="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Zone 11</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
+    </row>
+    <row r="14" ht="51.95" customFormat="1" customHeight="1" s="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Zone 12</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="n"/>
+      <c r="C14" s="8" t="n"/>
+    </row>
+    <row r="15" ht="51.95" customFormat="1" customHeight="1" s="1">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>Zone 13</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="n"/>
+      <c r="C15" s="19" t="n"/>
+    </row>
+    <row r="16" ht="51.95" customFormat="1" customHeight="1" s="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Zone 14</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="n"/>
+      <c r="C16" s="8" t="n"/>
+    </row>
+    <row r="17" ht="51.95" customFormat="1" customHeight="1" s="1">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>Zone 15</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="n"/>
+      <c r="C17" s="13" t="n"/>
+    </row>
+    <row r="18" ht="51.95" customFormat="1" customHeight="1" s="1">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>Zone 16</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="n"/>
+      <c r="C18" s="21" t="n"/>
+    </row>
+    <row r="19" ht="51.95" customFormat="1" customHeight="1" s="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Zone 17</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="23" t="n"/>
+    </row>
+    <row r="20" ht="51.95" customFormat="1" customHeight="1" s="1">
+      <c r="A20" s="25" t="inlineStr">
+        <is>
+          <t>Zone 18</t>
+        </is>
+      </c>
+      <c r="B20" s="26" t="n"/>
+      <c r="C20" s="26" t="n"/>
+    </row>
+    <row r="21" ht="51.95" customFormat="1" customHeight="1" s="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Zone 19</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="28" t="n"/>
+    </row>
+    <row r="22" ht="51.95" customFormat="1" customHeight="1" s="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Zone 20</t>
+        </is>
+      </c>
+      <c r="B22" s="30" t="n"/>
+      <c r="C22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="51.95" customFormat="1" customHeight="1" s="1">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>Zone 21</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="n"/>
+      <c r="C23" s="33" t="n"/>
+    </row>
+    <row r="24" ht="51.95" customFormat="1" customHeight="1" s="1">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>Zone 22</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="n"/>
+      <c r="C24" s="35" t="n"/>
+    </row>
+    <row r="25" ht="51.95" customFormat="1" customHeight="1" s="1">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Zone 23</t>
+        </is>
+      </c>
+      <c r="B25" s="37" t="n"/>
+      <c r="C25" s="28" t="n"/>
+    </row>
+    <row r="26" ht="51.95" customFormat="1" customHeight="1" s="1">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Zone 24</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="n"/>
+      <c r="C26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="51.95" customFormat="1" customHeight="1" s="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Zone 25</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="23" t="n"/>
+    </row>
+    <row r="28" ht="51.95" customFormat="1" customHeight="1" s="1">
+      <c r="A28" s="38" t="inlineStr">
+        <is>
+          <t>Zone 26</t>
+        </is>
+      </c>
+      <c r="B28" s="39" t="n"/>
+      <c r="C28" s="40" t="n"/>
+    </row>
+    <row r="29" ht="51.95" customFormat="1" customHeight="1" s="1">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Zone 27</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="51.95" customFormat="1" customHeight="1" s="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Zone 28</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="n"/>
+      <c r="C30" s="8" t="n"/>
+    </row>
+    <row r="31" ht="51.95" customFormat="1" customHeight="1" s="1">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Zone 29</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="51.95" customFormat="1" customHeight="1" s="1">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Zone 30</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="n"/>
+      <c r="C32" s="8" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" firstPageNumber="1" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
 </worksheet>
 </file>